--- a/DE_initiative_table.xlsx
+++ b/DE_initiative_table.xlsx
@@ -1,24 +1,238 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="" yWindow="" windowWidth="" windowHeight="" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Initiatives (Y1)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Named subrecipients" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OK vs DE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Initiatives (Y1)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reconciliation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Named subrecipients" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="OK vs DE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+  <si>
+    <t xml:space="preserve">DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Health Workforce Education Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contractors TBD (2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NON_HOSPITAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 1 contractual is entirely 'Legal Services for Service Commitment Agreements' ($450,000) and 'Program Oversight, Evaluation, Reporting' ($550,000), both 'Contractor: TBD'. Purpose: 'Provide educational awards to students in clinical training programs who commit to five years of practice in rural Delaware healthcare facilities.' Students receive the awards; rural facilities are the practice setting, not a funded party. No hospital named. PDF pp. 68-70.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1 (Dec 29 2025 - Oct 30 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final-RHTP-Revised-Budget-1.30.26.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Healthcare Workforce Data Center Initiative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Division of Professional Regulation (DPR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Name of Subrecipient: Division of Professional Regulation (DPR)' - a Delaware state agency. DPR 'may hire subcontractors for technical development, data integration, or cybersecurity support, but remains fully accountable'. No hospital receives funds; hospitals appear only as subjects of licensure-embedded workforce surveys. PDF pp. 71-72.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statewide Health IT Infrastructure for Prior Authorizations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statewide Health IT Infrastructure Vendor TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN_KIND_BENEFIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Contractor: TBD'. Scope: 'Integrate systems with Delaware Health Information Network (DHIN), Smart Health Network (SHN), participating payers, health systems, FQHCs, and rural providers' and 'Support onboarding and technical assistance for participating providers and payers, with priority given to rural healthcare organizations.' The vendor receives the funds; hospitals connect to and use the platform. Sec 10.2 IN_KIND_BENEFIT - hospital_benefiting, never a receipt. PDF pp. 73-74.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS FY2026 award to Delaware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published CMS figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget narrative TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches the award to the dollar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0.14 - rounding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal Direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of which Contractual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3% of direct costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnel + Fringe + Travel + Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiatives 1-15 + oversight captured here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 15 initiatives extracted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiatives 13-15 (extracted 2026-08-27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extracted from PDF pp. 68-74; equals Contractual less initiatives 1-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiatives 1-12 + oversight captured here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6% of captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiatives 13-15 (document truncated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8% of captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6% of captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital-directed (Yes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7% of captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unresolved (Unclear)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5% of captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-hospital (No)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.8% of captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dimension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oklahoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delaware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconciles to CMS award</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes - 91.7% allocated, 8.3% admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes - exact to the dollar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Names a recipient for every fund use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes - Lead Agency on all 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - 5 of 15 initiatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Names any hospital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital-directed share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7% of allocated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unclear share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital association involved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes - OHA administers $6.6M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largest single line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provider Collaborative Network $43.1M (hospital-owned nonprofit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical School $42.5M (not a hospital)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structured, repeating, one page per fund use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative, variable, contract-by-contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Statewide Health IT Infrastructure Vendor' - Contractor TBD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
@@ -31,19 +245,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <b/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -82,29 +297,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -461,25 +677,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="72" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="7" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="8" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="52" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="72" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="26" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="34" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1281,546 +1497,567 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J16" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2685200</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6420000</v>
+      </c>
+      <c r="E18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="46" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>157394964</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>157394963.86</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.139999985694885</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>144266694.65</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>143187467.48</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1079227.17000002</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>143187467.48</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10105200</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>20910000</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>32598772.48</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="n">
+        <v>89678695</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>20910000</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>32598772.48</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>79573495</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>named_subrecipient</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>initiative</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>amount_y1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recipient_type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>is_hospital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CMS FY2026 award to Delaware</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>157394964</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Published CMS figure</t>
+          <t>Delaware State Housing Authority</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Initiative 1 - Hope Center renovation</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>LOCAL_GOVT_OR_PUBLIC_HEALTH</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Budget narrative TOTAL</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>157394963.86</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Matches the award to the dollar</t>
+          <t>Delaware Division of Libraries</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Initiative 5 - Library operations</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>STATE_AGENCY</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Variance</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0.1399999856948853</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>$0.14 - rounding</t>
+          <t>Delaware Health Care Commission</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Initiative 10 - Med student awards</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>STATE_AGENCY</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Subtotal Direct</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>144266694.65</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  of which Contractual</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>143187467.48</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>99.3% of direct costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Personnel + Fringe + Travel + Supplies</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1079227.170000017</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>State admin</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Indirect (9.1%)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>13128269.21</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Initiatives 1-12 + oversight captured here</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>133082267.48</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Initiatives 13-15 (document truncated)</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>10105199.99999999</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Not extracted - ~7% of contractual</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Hospital-directed (Yes)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>20910000</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>15.7% of captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Unresolved (Unclear)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>32598772.48</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>24.5% of captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Non-hospital (No)</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>79573495</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>59.8% of captured</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Delaware Health Care Commission</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Initiative 11 - Residency recruitment</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1236495</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>STATE_AGENCY</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="52" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="52" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>named_subrecipient</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>initiative</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>amount_y1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>recipient_type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>is_hospital</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Delaware State Housing Authority</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Initiative 1 - Hope Center renovation</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>LOCAL_GOVT_OR_PUBLIC_HEALTH</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="A2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Delaware Division of Libraries</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Initiative 5 - Library operations</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>STATE_AGENCY</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Delaware Health Care Commission</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Initiative 10 - Med student awards</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>STATE_AGENCY</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Delaware Health Care Commission</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Initiative 11 - Residency recruitment</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1236495</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>STATE_AGENCY</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>dimension</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Delaware</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Reconciles to CMS award</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Yes - 91.7% allocated, 8.3% admin</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Yes - exact to the dollar</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Names a recipient for every fund use</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Yes - Lead Agency on all 28</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>No - 4 of 15 initiatives</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Names any hospital</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Hospital-directed share</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>48.7% of allocated</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>14.1% of captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Unclear share</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>43.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Hospital association involved</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Yes - OHA administers $6.6M</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Largest single line</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Provider Collaborative Network $43.1M (hospital-owned nonprofit)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Medical School $42.5M (not a hospital)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Document format</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Structured, repeating, one page per fund use</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Narrative, variable, contract-by-contract</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>